--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260708.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.82%</t>
+          <t>27.65%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.89%</t>
+          <t>8.70%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.42%</t>
+          <t>7.24%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.17%</t>
+          <t>6.10%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.64%</t>
+          <t>5.48%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -792,139 +792,139 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>205,316,499</t>
+          <t>20,783</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,783</t>
+          <t>22,455</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>22,455</t>
+          <t>35,780</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>35,780</t>
+          <t>147,491,691</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>57,965</t>
+          <t>22,995</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>22,995</t>
+          <t>57,965</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -946,51 +946,51 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>30,178</t>
+          <t>9,090</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,090</t>
+          <t>30,178</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1056,29 +1056,29 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>24,158</t>
+          <t>13,251</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1100,73 +1100,73 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>13,251</t>
+          <t>24,158</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>143,615</t>
+          <t>20,935</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>20,935</t>
+          <t>143,615</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1188,68 +1188,68 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>42,540</t>
+          <t>22,387</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>22,387</t>
+          <t>1,925,386</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,305</t>
+          <t>42,540</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,44 +1261,44 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>48,940</t>
+          <t>13,305</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,317,683</t>
+          <t>48,940</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1315,32 +1315,10 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>22,471,200</t>
+          <t>9,642,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>1,007,703</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
